--- a/Horarios/Trenes/Catan-Lozano/SabadoCatan.xlsx
+++ b/Horarios/Trenes/Catan-Lozano/SabadoCatan.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Horarios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Horarios" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -15,136 +15,140 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:styleSheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <ns0:numFmts count="1">
-    <ns0:numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-  </ns0:numFmts>
-  <ns0:fonts count="3">
-    <ns0:font>
-      <ns0:sz val="11"/>
-      <ns0:color theme="1"/>
-      <ns0:name val="Calibri"/>
-    </ns0:font>
-    <ns0:font>
-      <ns0:sz val="11"/>
-      <ns0:name val="Aptos Narrow"/>
-    </ns0:font>
-    <ns0:font>
-      <ns0:sz val="12"/>
-      <ns0:color theme="10"/>
-      <ns0:name val="Calibri"/>
-    </ns0:font>
-  </ns0:fonts>
-  <ns0:fills count="2">
-    <ns0:fill>
-      <ns0:patternFill/>
-    </ns0:fill>
-    <ns0:fill>
-      <ns0:patternFill patternType="gray125"/>
-    </ns0:fill>
-  </ns0:fills>
-  <ns0:borders count="1">
-    <ns0:border>
-      <ns0:left/>
-      <ns0:right/>
-      <ns0:top/>
-      <ns0:bottom/>
-      <ns0:diagonal/>
-    </ns0:border>
-  </ns0:borders>
-  <ns0:cellStyleXfs count="2">
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <ns0:xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-  </ns0:cellStyleXfs>
-  <ns0:cellXfs count="5">
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <ns0:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="20" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <ns0:alignment horizontal="left" vertical="center"/>
-    </ns0:xf>
-  </ns0:cellXfs>
-  <ns0:cellStyles count="2">
-    <ns0:cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
-    <ns0:cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
-  </ns0:cellStyles>
-  <ns0:tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <ns0:colors>
-    <ns0:indexedColors>
-      <ns0:rgbColor rgb="00000000"/>
-      <ns0:rgbColor rgb="00FFFFFF"/>
-      <ns0:rgbColor rgb="00FF0000"/>
-      <ns0:rgbColor rgb="0000FF00"/>
-      <ns0:rgbColor rgb="000000FF"/>
-      <ns0:rgbColor rgb="00FFFF00"/>
-      <ns0:rgbColor rgb="00FF00FF"/>
-      <ns0:rgbColor rgb="0000FFFF"/>
-      <ns0:rgbColor rgb="00000000"/>
-      <ns0:rgbColor rgb="00FFFFFF"/>
-      <ns0:rgbColor rgb="00FF0000"/>
-      <ns0:rgbColor rgb="0000FF00"/>
-      <ns0:rgbColor rgb="000000FF"/>
-      <ns0:rgbColor rgb="00FFFF00"/>
-      <ns0:rgbColor rgb="00FF00FF"/>
-      <ns0:rgbColor rgb="0000FFFF"/>
-      <ns0:rgbColor rgb="00800000"/>
-      <ns0:rgbColor rgb="00008000"/>
-      <ns0:rgbColor rgb="00000080"/>
-      <ns0:rgbColor rgb="00808000"/>
-      <ns0:rgbColor rgb="00800080"/>
-      <ns0:rgbColor rgb="00008080"/>
-      <ns0:rgbColor rgb="00C0C0C0"/>
-      <ns0:rgbColor rgb="00808080"/>
-      <ns0:rgbColor rgb="009999FF"/>
-      <ns0:rgbColor rgb="00993366"/>
-      <ns0:rgbColor rgb="00FFFFCC"/>
-      <ns0:rgbColor rgb="00CCFFFF"/>
-      <ns0:rgbColor rgb="00660066"/>
-      <ns0:rgbColor rgb="00FF8080"/>
-      <ns0:rgbColor rgb="000066CC"/>
-      <ns0:rgbColor rgb="00CCCCFF"/>
-      <ns0:rgbColor rgb="00000080"/>
-      <ns0:rgbColor rgb="00FF00FF"/>
-      <ns0:rgbColor rgb="00FFFF00"/>
-      <ns0:rgbColor rgb="0000FFFF"/>
-      <ns0:rgbColor rgb="00800080"/>
-      <ns0:rgbColor rgb="00800000"/>
-      <ns0:rgbColor rgb="00008080"/>
-      <ns0:rgbColor rgb="000000FF"/>
-      <ns0:rgbColor rgb="0000CCFF"/>
-      <ns0:rgbColor rgb="00CCFFFF"/>
-      <ns0:rgbColor rgb="00CCFFCC"/>
-      <ns0:rgbColor rgb="00FFFF99"/>
-      <ns0:rgbColor rgb="0099CCFF"/>
-      <ns0:rgbColor rgb="00FF99CC"/>
-      <ns0:rgbColor rgb="00CC99FF"/>
-      <ns0:rgbColor rgb="00FFCC99"/>
-      <ns0:rgbColor rgb="003366FF"/>
-      <ns0:rgbColor rgb="0033CCCC"/>
-      <ns0:rgbColor rgb="0099CC00"/>
-      <ns0:rgbColor rgb="00FFCC00"/>
-      <ns0:rgbColor rgb="00FF9900"/>
-      <ns0:rgbColor rgb="00FF6600"/>
-      <ns0:rgbColor rgb="00666699"/>
-      <ns0:rgbColor rgb="00969696"/>
-      <ns0:rgbColor rgb="00003366"/>
-      <ns0:rgbColor rgb="00339966"/>
-      <ns0:rgbColor rgb="00003300"/>
-      <ns0:rgbColor rgb="00333300"/>
-      <ns0:rgbColor rgb="00993300"/>
-      <ns0:rgbColor rgb="00993366"/>
-      <ns0:rgbColor rgb="00333399"/>
-      <ns0:rgbColor rgb="00333333"/>
-    </ns0:indexedColors>
-  </ns0:colors>
-</ns0:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="3">
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
+  </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -508,23 +512,29 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>5302</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>0.4701388888888889</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.4881944444444444</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0.5090277777777777</v>
+          <t>59102</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.525</v>
+        <v>0.4243055555555555</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.5388888888888889</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="3">
@@ -535,7 +545,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>59104</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
@@ -548,14 +558,16 @@
           <t>null</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>0.5951388888888889</v>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.5</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.625</v>
+        <v>0.5131944444444444</v>
       </c>
     </row>
     <row r="4">
@@ -566,23 +578,29 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>5306</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>0.7166666666666667</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.7347222222222223</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0.7555555555555555</v>
+          <t>59106</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.7715277777777778</v>
+        <v>0.6777777777777778</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.7854166666666667</v>
+        <v>0.6909722222222222</v>
       </c>
     </row>
     <row r="5">
@@ -593,7 +611,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>59108</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -606,14 +624,16 @@
           <t>null</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>0.8298611111111112</v>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.8458333333333333</v>
+        <v>0.7569444444444444</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.8597222222222223</v>
+        <v>0.7701388888888889</v>
       </c>
     </row>
     <row r="6">
@@ -770,7 +790,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46263</v>
+        <v>46305</v>
       </c>
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="1" t="n"/>

--- a/Horarios/Trenes/Catan-Lozano/SabadoCatan.xlsx
+++ b/Horarios/Trenes/Catan-Lozano/SabadoCatan.xlsx
@@ -512,29 +512,23 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>59102</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0.4701388888888889</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.4881944444444444</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.5090277777777777</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.4243055555555555</v>
+        <v>0.525</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.4375</v>
+        <v>0.5388888888888889</v>
       </c>
     </row>
     <row r="3">
@@ -545,7 +539,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>59104</t>
+          <t>5204</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
@@ -558,16 +552,14 @@
           <t>null</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
+      <c r="E3" s="2" t="n">
+        <v>0.5951388888888889</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.5131944444444444</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="4">
@@ -578,29 +570,23 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>59106</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0.7166666666666667</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.7347222222222223</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.7555555555555555</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.6777777777777778</v>
+        <v>0.7715277777777778</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.6909722222222222</v>
+        <v>0.7854166666666667</v>
       </c>
     </row>
     <row r="5">
@@ -611,7 +597,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>59108</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -624,16 +610,14 @@
           <t>null</t>
         </is>
       </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
+      <c r="E5" s="2" t="n">
+        <v>0.8298611111111112</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.7569444444444444</v>
+        <v>0.8458333333333333</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.7701388888888889</v>
+        <v>0.8597222222222223</v>
       </c>
     </row>
     <row r="6">
@@ -790,7 +774,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46305</v>
+        <v>46312</v>
       </c>
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="1" t="n"/>

--- a/Horarios/Trenes/Catan-Lozano/SabadoCatan.xlsx
+++ b/Horarios/Trenes/Catan-Lozano/SabadoCatan.xlsx
@@ -512,23 +512,29 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>5302</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>0.4701388888888889</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.4881944444444444</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0.5090277777777777</v>
+          <t>59102</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.525</v>
+        <v>0.4243055555555555</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.5388888888888889</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="3">
@@ -539,7 +545,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>59104</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
@@ -552,14 +558,16 @@
           <t>null</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>0.5951388888888889</v>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.5</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.625</v>
+        <v>0.5131944444444444</v>
       </c>
     </row>
     <row r="4">
@@ -570,23 +578,29 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>5306</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>0.7166666666666667</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.7347222222222223</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0.7555555555555555</v>
+          <t>59106</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.7715277777777778</v>
+        <v>0.6777777777777778</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.7854166666666667</v>
+        <v>0.6909722222222222</v>
       </c>
     </row>
     <row r="5">
@@ -597,7 +611,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>59108</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -610,14 +624,16 @@
           <t>null</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>0.8298611111111112</v>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.8458333333333333</v>
+        <v>0.7569444444444444</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.8597222222222223</v>
+        <v>0.7701388888888889</v>
       </c>
     </row>
     <row r="6">

--- a/Horarios/Trenes/Catan-Lozano/SabadoCatan.xlsx
+++ b/Horarios/Trenes/Catan-Lozano/SabadoCatan.xlsx
@@ -512,29 +512,23 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>59102</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0.4701388888888889</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.4881944444444444</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.5090277777777777</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.4243055555555555</v>
+        <v>0.525</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.4375</v>
+        <v>0.5388888888888889</v>
       </c>
     </row>
     <row r="3">
@@ -545,7 +539,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>59104</t>
+          <t>5204</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
@@ -558,16 +552,14 @@
           <t>null</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
+      <c r="E3" s="2" t="n">
+        <v>0.5951388888888889</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.5131944444444444</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="4">
@@ -578,29 +570,23 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>59106</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0.7166666666666667</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.7347222222222223</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.7555555555555555</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.6777777777777778</v>
+        <v>0.7715277777777778</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.6909722222222222</v>
+        <v>0.7854166666666667</v>
       </c>
     </row>
     <row r="5">
@@ -611,7 +597,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>59108</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -624,16 +610,14 @@
           <t>null</t>
         </is>
       </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
+      <c r="E5" s="2" t="n">
+        <v>0.8298611111111112</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.7569444444444444</v>
+        <v>0.8458333333333333</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.7701388888888889</v>
+        <v>0.8597222222222223</v>
       </c>
     </row>
     <row r="6">
@@ -790,7 +774,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46312</v>
+        <v>46319</v>
       </c>
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="1" t="n"/>
